--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513277_ELIMINGRB12FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513277_ELIMINGRB12FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2296</v>
+        <v>3.2864</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1663</v>
+        <v>1.5631</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0632</v>
+        <v>1.7233</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0509</v>
+        <v>2.0748</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1225</v>
+        <v>-0.1006</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1734</v>
+        <v>2.1753</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4672</v>
+        <v>1.5983</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4145</v>
+        <v>-0.3309</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8816</v>
+        <v>1.9292</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5837</v>
+        <v>0.4765</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2919</v>
+        <v>0.2303</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2918</v>
+        <v>0.2461</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1812</v>
+        <v>-0.1599</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5601</v>
+        <v>-0.3673</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3789</v>
+        <v>0.2074</v>
       </c>
       <c r="V2" t="n">
-        <v>1.76</v>
+        <v>1.7611</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3004</v>
+        <v>0.2605</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3</v>
+        <v>1.1565</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0723</v>
+        <v>2.2377</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7723</v>
+        <v>-1.0812</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7514</v>
+        <v>2.7403</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9536</v>
+        <v>0.9411</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7978</v>
+        <v>1.7992</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8595</v>
+        <v>2.91</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9397</v>
+        <v>0.9647</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9197</v>
+        <v>1.9453</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1081</v>
+        <v>-0.1697</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0138</v>
+        <v>-0.0236</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1219</v>
+        <v>-0.146</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5285</v>
+        <v>0.4019</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3867</v>
+        <v>-0.3092</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9153</v>
+        <v>0.7111</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9797</v>
+        <v>-1.0121</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5795</v>
+        <v>-1.6226</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6944</v>
+        <v>0.5311</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4326</v>
+        <v>1.6253</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7381</v>
+        <v>-1.0942</v>
       </c>
       <c r="G4" t="n">
-        <v>0.296</v>
+        <v>0.2659</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4978</v>
+        <v>1.5061</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2017</v>
+        <v>-1.2402</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7395</v>
+        <v>1.7842</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6195</v>
+        <v>1.6626</v>
       </c>
       <c r="L4" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4435</v>
+        <v>-1.5184</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1218</v>
+        <v>-0.1565</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3217</v>
+        <v>-1.3618</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>0.058</v>
+        <v>-0.0395</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5667</v>
+        <v>-0.4384</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6247</v>
+        <v>0.3989</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>P. LOPEZ USO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1409</v>
+        <v>0.0984</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9216</v>
+        <v>0.0552</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0625</v>
+        <v>0.0431</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.562</v>
+        <v>0.8401</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1382</v>
+        <v>0.5111</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.7002</v>
+        <v>0.329</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.2885</v>
+        <v>1.3925</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3035</v>
+        <v>0.0873</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.592</v>
+        <v>1.3052</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2735</v>
+        <v>-0.5525</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1654</v>
+        <v>0.4238</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1082</v>
+        <v>-0.9762</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6005</v>
+        <v>0.9737</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4007</v>
+        <v>-0.1947</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8002</v>
+        <v>1.1684</v>
       </c>
       <c r="S5" t="n">
-        <v>1.065</v>
+        <v>-0.7033</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4092</v>
+        <v>-1.1426</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6558</v>
+        <v>0.4393</v>
       </c>
       <c r="V5" t="n">
-        <v>3.2384</v>
+        <v>-1.0121</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3584</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.12</v>
+        <v>-1.0121</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0761</v>
+        <v>0.0098</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3033</v>
+        <v>-1.13</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2273</v>
+        <v>1.1398</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7985</v>
+        <v>1.7506</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6962</v>
+        <v>0.6516</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1023</v>
+        <v>1.099</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0217</v>
+        <v>1.0623</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3399</v>
+        <v>0.3489</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6818</v>
+        <v>0.7134</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7768</v>
+        <v>0.6883</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3563</v>
+        <v>0.3027</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1941</v>
+        <v>-0.105</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4445</v>
+        <v>-0.3618</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2504</v>
+        <v>0.2568</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. LOPEZ USO</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4562</v>
+        <v>-0.5868</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.402</v>
+        <v>-1.2347</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0542</v>
+        <v>0.6479</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8648</v>
+        <v>-2.5853</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5224</v>
+        <v>0.1103</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3424</v>
+        <v>-2.6956</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2672</v>
+        <v>-2.1618</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0236</v>
+        <v>0.3747</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2436</v>
+        <v>-2.5364</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4024</v>
+        <v>-0.4235</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4988</v>
+        <v>-0.2644</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9012</v>
+        <v>-0.1591</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0003</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2001</v>
+        <v>-2.3368</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2003</v>
+        <v>0.7789</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3417</v>
+        <v>0.17</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4691</v>
+        <v>-0.2446</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1275</v>
+        <v>0.4146</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9797</v>
+        <v>3.3863</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.5084</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9797</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5438</v>
+        <v>-1.2632</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3836</v>
+        <v>-0.1582</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1602</v>
+        <v>-1.1049</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8536</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3981</v>
+        <v>-0.3771</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4556</v>
+        <v>-0.4571</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5255</v>
+        <v>0.617</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0764</v>
+        <v>-0.0153</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6018</v>
+        <v>0.6323</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3791</v>
+        <v>-1.4513</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3217</v>
+        <v>-0.3618</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0574</v>
+        <v>-1.0895</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8902</v>
+        <v>-0.6237</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.709</v>
+        <v>-0.5805</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1812</v>
+        <v>-0.0432</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5506</v>
+        <v>-2.0433</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9927</v>
+        <v>-1.3278</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5579</v>
+        <v>-0.7155</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3575</v>
+        <v>0.3789</v>
       </c>
       <c r="H9" t="n">
-        <v>2.612</v>
+        <v>2.5554</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2545</v>
+        <v>-2.1765</v>
       </c>
       <c r="J9" t="n">
-        <v>0.075</v>
+        <v>0.2787</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6995</v>
+        <v>1.7447</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6245</v>
+        <v>-1.466</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2825</v>
+        <v>0.1002</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9125</v>
+        <v>0.8107</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.63</v>
+        <v>-0.7104</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1681</v>
+        <v>-0.6753</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5269</v>
+        <v>-1.1333</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3588</v>
+        <v>0.458</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5399</v>
+        <v>-1.5521</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7036</v>
+        <v>-2.1613</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8701</v>
+        <v>-3.5303</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1665</v>
+        <v>1.369</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.641</v>
+        <v>-0.7325</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5344</v>
+        <v>0.454</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1755</v>
+        <v>-1.1866</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7741</v>
+        <v>-1.7288</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1</v>
+        <v>0.1026</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.874</v>
+        <v>-1.8314</v>
       </c>
       <c r="M10" t="n">
-        <v>1.133</v>
+        <v>0.9962</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4345</v>
+        <v>0.3514</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6986</v>
+        <v>0.6448</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1423</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.6331</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2466</v>
+        <v>0.1054</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0841</v>
+        <v>-4.3861</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2457</v>
+        <v>-3.1443</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8384</v>
+        <v>-1.2418</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3159</v>
+        <v>-2.2995</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3316</v>
+        <v>-1.2977</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9842</v>
+        <v>-1.0018</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5941</v>
+        <v>-1.543</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6741</v>
+        <v>-1.624</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7218</v>
+        <v>-0.7565</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3425</v>
+        <v>0.3263</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0642</v>
+        <v>-1.0829</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2318</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4512</v>
+        <v>-0.4328</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.3463</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0495</v>
+        <v>-5.358499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.447799999999999</v>
+        <v>-5.044</v>
       </c>
       <c r="F12" t="n">
-        <v>1.398400000000001</v>
+        <v>-0.3145</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7466</v>
+        <v>1.5991</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1024</v>
+        <v>4.9542</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3558</v>
+        <v>-3.355300000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>3.298900000000001</v>
+        <v>4.2094</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8607</v>
+        <v>3.3153</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4380000000000001</v>
+        <v>0.8943000000000005</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5524</v>
+        <v>-2.6107</v>
       </c>
       <c r="N12" t="n">
-        <v>2.2414</v>
+        <v>1.6389</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.7937</v>
+        <v>-4.2494</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.0028</v>
+        <v>-9.736700000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>6.0016</v>
+        <v>5.842000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.0343</v>
+        <v>-2.349</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.6007</v>
+        <v>-5.6436</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5666</v>
+        <v>3.2946</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7606999999999996</v>
+        <v>-0.7137000000000003</v>
       </c>
       <c r="W12" t="n">
-        <v>5.8572</v>
+        <v>6.126799999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.6177</v>
+        <v>-6.8406</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4072</v>
+        <v>5.3259</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3547</v>
+        <v>4.0475</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0525</v>
+        <v>1.2785</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1643</v>
+        <v>4.1895</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1179</v>
+        <v>1.1161</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0464</v>
+        <v>3.0734</v>
       </c>
       <c r="J13" t="n">
-        <v>4.0448</v>
+        <v>4.196</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5614</v>
+        <v>1.6344</v>
       </c>
       <c r="L13" t="n">
-        <v>2.4835</v>
+        <v>2.5615</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1195</v>
+        <v>-0.0064</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4435</v>
+        <v>-0.5184</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5119</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4648</v>
+        <v>0.4049</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0891</v>
+        <v>-0.6433</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6243</v>
+        <v>1.0482</v>
       </c>
       <c r="V13" t="n">
-        <v>1.708</v>
+        <v>1.7052</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6915</v>
+        <v>-0.737</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0021</v>
+        <v>2.9629</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6266</v>
+        <v>1.1563</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3755</v>
+        <v>1.8066</v>
       </c>
       <c r="G14" t="n">
-        <v>1.666</v>
+        <v>1.721</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8467</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8193</v>
+        <v>0.8707</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6889</v>
+        <v>2.8591</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9615</v>
+        <v>1.0187</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7274</v>
+        <v>1.8404</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0229</v>
+        <v>-1.138</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1149</v>
+        <v>-0.1684</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9081</v>
+        <v>-0.9697</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7678</v>
+        <v>0.6993</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.062</v>
+        <v>-0.7291</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8299</v>
+        <v>1.4284</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1682</v>
+        <v>0.1531</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1682</v>
+        <v>0.1531</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1871</v>
+        <v>1.8918</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6878</v>
+        <v>1.4058</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4993</v>
+        <v>0.486</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4752</v>
+        <v>1.5124</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1171</v>
+        <v>1.1721</v>
       </c>
       <c r="I15" t="n">
-        <v>0.358</v>
+        <v>0.3403</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9052</v>
+        <v>1.0228</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5032</v>
+        <v>1.6063</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M15" t="n">
-        <v>0.57</v>
+        <v>0.4896</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3861</v>
+        <v>-0.4342</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9237</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3228</v>
+        <v>1.0911</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7826</v>
+        <v>0.383</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5402</v>
+        <v>0.7081</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2111</v>
+        <v>-1.2959</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2111</v>
+        <v>-1.2959</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5452</v>
+        <v>1.2991</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2744</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2707</v>
+        <v>1.2044</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1931</v>
+        <v>-0.2113</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.838</v>
+        <v>-0.8287</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6449</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0437</v>
+        <v>0.0978</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.6722</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7599</v>
+        <v>0.77</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2368</v>
+        <v>-0.3091</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1218</v>
+        <v>-0.1565</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.115</v>
+        <v>-0.1526</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4782</v>
+        <v>0.2573</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2889</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.767</v>
+        <v>0.8193</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4914</v>
+        <v>1.0271</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2903</v>
+        <v>0.4589</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7817</v>
+        <v>0.5682</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7422</v>
+        <v>-0.63</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.0514</v>
+        <v>0.2842</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3093</v>
+        <v>-0.9142</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2342</v>
+        <v>0.1515</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3942</v>
+        <v>0.1026</v>
       </c>
       <c r="L17" t="n">
-        <v>0.16</v>
+        <v>0.0489</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5079</v>
+        <v>-0.7815</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6573</v>
+        <v>0.1816</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1493</v>
+        <v>-0.9631</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4001</v>
+        <v>0.9737</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3738</v>
+        <v>-0.2582</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5157</v>
+        <v>-0.9137</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8895</v>
+        <v>0.6555</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4596</v>
+        <v>0.9416</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4596</v>
+        <v>1.2211</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3367</v>
+        <v>0.4823</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1433</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1933</v>
+        <v>0.5513</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5974</v>
+        <v>-1.7548</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3137</v>
+        <v>-2.0367</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9111</v>
+        <v>0.2819</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1038</v>
+        <v>-1.1746</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1</v>
+        <v>-1.3367</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0038</v>
+        <v>0.1621</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.5802</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2138</v>
+        <v>-0.7</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9149</v>
+        <v>0.1198</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0003</v>
+        <v>0.3895</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0003</v>
+        <v>0.3895</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0062</v>
+        <v>0.347</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1602</v>
+        <v>-0.395</v>
       </c>
       <c r="U18" t="n">
-        <v>0.154</v>
+        <v>0.742</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.5005</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1998</v>
+        <v>1.5005</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0321</v>
+        <v>0.2393</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1429</v>
+        <v>-0.0702</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1109</v>
+        <v>0.3096</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7267</v>
+        <v>0.7266</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2625</v>
+        <v>-0.2442</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9892</v>
+        <v>0.9708</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0418</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0018</v>
+        <v>0.0334</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6849</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9492</v>
+        <v>0.9303</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5813</v>
+        <v>0.8438</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5558</v>
+        <v>0.5501</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0255</v>
+        <v>0.2937</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9416</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="20">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9051</v>
+        <v>-0.2047</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.416</v>
+        <v>-0.8067</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5108</v>
+        <v>0.602</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.746</v>
+        <v>-1.6402</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5411</v>
+        <v>-1.4685</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2049</v>
+        <v>-0.1716</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9667</v>
+        <v>-0.8047</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4124</v>
+        <v>-1.3238</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4456</v>
+        <v>0.5191</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7793</v>
+        <v>-0.8355</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1287</v>
+        <v>-0.1447</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6506</v>
+        <v>-0.6907</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4192</v>
+        <v>0.1823</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.709</v>
+        <v>-0.2815</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2898</v>
+        <v>0.4638</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3531</v>
+        <v>-0.9589</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0251</v>
+        <v>-1.4634</v>
       </c>
       <c r="F21" t="n">
-        <v>0.672</v>
+        <v>0.5046</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3484</v>
+        <v>-1.3874</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1709</v>
+        <v>-1.1895</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1775</v>
+        <v>-0.1979</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.176</v>
+        <v>-1.1453</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.578</v>
+        <v>-0.5619</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1724</v>
+        <v>-0.242</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5929</v>
+        <v>-0.6276</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4205</v>
+        <v>0.3856</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1351</v>
+        <v>0.5911</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.509</v>
+        <v>0.0129</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6441</v>
+        <v>0.5782</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9416</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1893</v>
+        <v>-1.1464</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7405</v>
+        <v>-2.1912</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5512</v>
+        <v>1.0448</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.7961</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2174</v>
+        <v>-0.2484</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5805</v>
+        <v>-0.5477</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3105</v>
+        <v>-0.1962</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2381</v>
+        <v>-0.2129</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.07240000000000001</v>
+        <v>0.0167</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4874</v>
+        <v>-0.5999</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0207</v>
+        <v>-0.0355</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5081</v>
+        <v>-0.5644</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0191</v>
+        <v>-0.0039</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2891</v>
+        <v>-0.9377</v>
       </c>
       <c r="U22" t="n">
-        <v>0.27</v>
+        <v>0.9338</v>
       </c>
       <c r="V22" t="n">
-        <v>0.428</v>
+        <v>0.4325</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4317</v>
+        <v>-0.4575</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4406</v>
+        <v>-2.9482</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8703</v>
+        <v>-2.2482</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5704</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3538</v>
+        <v>-3.3288</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4164</v>
+        <v>-2.3609</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9374</v>
+        <v>-0.9679</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.5884</v>
+        <v>-2.4697</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.0304</v>
+        <v>-1.9267</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5429</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7654</v>
+        <v>-0.8591</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3861</v>
+        <v>-0.4342</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3794</v>
+        <v>-0.4249</v>
       </c>
       <c r="P23" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2846</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7181</v>
+        <v>0.2215</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5665</v>
+        <v>0.5844</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.3717</v>
+        <v>-1.3991</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.3717</v>
+        <v>-1.3991</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.049500000000002</v>
+        <v>7.970200000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3983</v>
+        <v>0.3144999999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>7.447500000000001</v>
+        <v>7.6559</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.746600000000001</v>
+        <v>-1.5991</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.1023</v>
+        <v>-4.9542</v>
       </c>
       <c r="I24" t="n">
-        <v>3.355700000000001</v>
+        <v>3.3552</v>
       </c>
       <c r="J24" t="n">
-        <v>1.5524</v>
+        <v>2.610599999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.241400000000001</v>
+        <v>-1.6388</v>
       </c>
       <c r="L24" t="n">
-        <v>3.7938</v>
+        <v>4.2493</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.2988</v>
+        <v>-4.2094</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.8611</v>
+        <v>-3.3155</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4380000000000001</v>
+        <v>-0.8941</v>
       </c>
       <c r="P24" t="n">
-        <v>4.0012</v>
+        <v>3.8948</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.001799999999999</v>
+        <v>-5.8422</v>
       </c>
       <c r="R24" t="n">
-        <v>10.0029</v>
+        <v>9.736900000000002</v>
       </c>
       <c r="S24" t="n">
-        <v>3.0343</v>
+        <v>4.9606</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.5665</v>
+        <v>-3.2948</v>
       </c>
       <c r="U24" t="n">
-        <v>6.6008</v>
+        <v>8.2554</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7605999999999999</v>
+        <v>0.7137</v>
       </c>
       <c r="W24" t="n">
-        <v>6.617700000000001</v>
+        <v>6.8406</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.8571</v>
+        <v>-6.127</v>
       </c>
     </row>
   </sheetData>
